--- a/datasets/day1_excel_foundations/04_formulas_fundamentals/d1_m4_formulas_start.xlsx
+++ b/datasets/day1_excel_foundations/04_formulas_fundamentals/d1_m4_formulas_start.xlsx
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>119.7</v>
+        <v>120</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>1</v>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>1666</v>
+        <v>1500</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>2</v>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>1454.4</v>
+        <v>1400</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>806</v>
+        <v>600</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>1</v>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>828</v>
+        <v>800</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2</v>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>108.75</v>
+        <v>100</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>3</v>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>779.2</v>
+        <v>1000</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>1</v>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>587.2</v>
+        <v>600</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>1</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>801.6</v>
+        <v>1200</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>1</v>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>1663</v>
+        <v>1400</v>
       </c>
       <c r="D17" s="7" t="n">
         <v>1</v>
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1037</v>
+        <v>600</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>1</v>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>724</v>
+        <v>800</v>
       </c>
       <c r="D19" s="7" t="n">
         <v>1</v>
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>177</v>
+        <v>100</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>1</v>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>653.8</v>
+        <v>800</v>
       </c>
       <c r="D21" s="7" t="n">
         <v>1</v>
@@ -932,7 +932,7 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>1758</v>
+        <v>1400</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>1</v>
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>56.1</v>
+        <v>120</v>
       </c>
       <c r="D23" s="7" t="n">
         <v>1</v>
@@ -978,7 +978,7 @@
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>1148</v>
+        <v>1400</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>1</v>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>905.25</v>
+        <v>1400</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>1</v>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>918</v>
+        <v>600</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>1</v>

--- a/datasets/day1_excel_foundations/04_formulas_fundamentals/d1_m4_formulas_start.xlsx
+++ b/datasets/day1_excel_foundations/04_formulas_fundamentals/d1_m4_formulas_start.xlsx
@@ -636,7 +636,7 @@
         <v>1500</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="6" t="n"/>
@@ -659,7 +659,7 @@
         <v>1400</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
@@ -675,11 +675,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OnePlus 13</t>
+          <t>iPad Air 6</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>1</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>Ring Doorbell Pro</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2</v>
@@ -721,14 +721,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Echo Dot 6</t>
+          <t>Galaxy S24</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n"/>
@@ -767,14 +767,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Surface Go 4</t>
+          <t>USB-C Hub 7in1</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>600</v>
+        <v>80</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
@@ -790,14 +790,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HP Spectre x360</t>
+          <t>Surface Go 4</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="n"/>
@@ -813,14 +813,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>Pixel 9 Pro</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>1400</v>
+        <v>900</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="n"/>
@@ -836,11 +836,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Surface Go 4</t>
+          <t>Echo Dot 6</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>1</v>
@@ -859,14 +859,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>HP Spectre x360</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="6" t="n"/>
       <c r="F19" s="6" t="n"/>
@@ -882,11 +882,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Echo Dot 6</t>
+          <t>Galaxy Tab S10</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>1</v>
@@ -905,11 +905,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>Wireless Mouse Pro</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>800</v>
+        <v>60</v>
       </c>
       <c r="D21" s="7" t="n">
         <v>1</v>
@@ -928,11 +928,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>OnePlus 13</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>1400</v>
+        <v>600</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>1</v>
@@ -951,11 +951,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bluetooth Headphones</t>
+          <t>Google Nest Hub 3</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="D23" s="7" t="n">
         <v>1</v>
@@ -974,14 +974,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>Laptop Sleeve 15in</t>
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>1400</v>
+        <v>50</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24" s="6" t="n"/>
       <c r="F24" s="6" t="n"/>
@@ -997,14 +997,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>iPad Air 6</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>1400</v>
+        <v>700</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="6" t="n"/>
       <c r="F25" s="6" t="n"/>
@@ -1020,11 +1020,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>OnePlus 13</t>
+          <t>Ring Doorbell Pro</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>1</v>
